--- a/sources/table_normalization/xlsx/education-table27.xlsx
+++ b/sources/table_normalization/xlsx/education-table27.xlsx
@@ -78,7 +78,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -97,12 +97,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -118,7 +112,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -126,8 +120,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -696,7 +688,7 @@
       <c r="AA1" s="1">
         <v>24</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AB1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -782,7 +774,7 @@
       <c r="AA2" s="2">
         <v>2</v>
       </c>
-      <c r="AB2" s="6">
+      <c r="AB2" s="2">
         <f t="shared" ref="AB2:AB37" si="0">SUM(D2:AA2)</f>
         <v>46</v>
       </c>
@@ -869,7 +861,7 @@
       <c r="AA3" s="2">
         <v>-2</v>
       </c>
-      <c r="AB3" s="6">
+      <c r="AB3" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -956,7 +948,7 @@
       <c r="AA4" s="2">
         <v>2</v>
       </c>
-      <c r="AB4" s="6">
+      <c r="AB4" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -1043,7 +1035,7 @@
       <c r="AA5" s="2">
         <v>2</v>
       </c>
-      <c r="AB5" s="6">
+      <c r="AB5" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -1130,7 +1122,7 @@
       <c r="AA6" s="2">
         <v>1</v>
       </c>
-      <c r="AB6" s="6">
+      <c r="AB6" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
@@ -1217,7 +1209,7 @@
       <c r="AA7" s="2">
         <v>2</v>
       </c>
-      <c r="AB7" s="6">
+      <c r="AB7" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
@@ -1304,7 +1296,7 @@
       <c r="AA8" s="2">
         <v>1</v>
       </c>
-      <c r="AB8" s="6">
+      <c r="AB8" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
@@ -1391,7 +1383,7 @@
       <c r="AA9" s="2">
         <v>3</v>
       </c>
-      <c r="AB9" s="6">
+      <c r="AB9" s="2">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
@@ -1478,7 +1470,7 @@
       <c r="AA10" s="2">
         <v>0</v>
       </c>
-      <c r="AB10" s="6">
+      <c r="AB10" s="2">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
@@ -1565,7 +1557,7 @@
       <c r="AA11" s="2">
         <v>2</v>
       </c>
-      <c r="AB11" s="6">
+      <c r="AB11" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
@@ -1652,7 +1644,7 @@
       <c r="AA12" s="2">
         <v>3</v>
       </c>
-      <c r="AB12" s="6">
+      <c r="AB12" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -1739,7 +1731,7 @@
       <c r="AA13" s="2">
         <v>2</v>
       </c>
-      <c r="AB13" s="6">
+      <c r="AB13" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
@@ -1826,7 +1818,7 @@
       <c r="AA14" s="2">
         <v>-1</v>
       </c>
-      <c r="AB14" s="6">
+      <c r="AB14" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
@@ -1913,7 +1905,7 @@
       <c r="AA15" s="2">
         <v>1</v>
       </c>
-      <c r="AB15" s="6">
+      <c r="AB15" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -2000,7 +1992,7 @@
       <c r="AA16" s="2">
         <v>1</v>
       </c>
-      <c r="AB16" s="6">
+      <c r="AB16" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
@@ -2087,7 +2079,7 @@
       <c r="AA17" s="2">
         <v>0</v>
       </c>
-      <c r="AB17" s="6">
+      <c r="AB17" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
@@ -2174,7 +2166,7 @@
       <c r="AA18" s="2">
         <v>4</v>
       </c>
-      <c r="AB18" s="6">
+      <c r="AB18" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -2261,7 +2253,7 @@
       <c r="AA19" s="2">
         <v>0</v>
       </c>
-      <c r="AB19" s="6">
+      <c r="AB19" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
@@ -2348,7 +2340,7 @@
       <c r="AA20" s="2">
         <v>0</v>
       </c>
-      <c r="AB20" s="6">
+      <c r="AB20" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
@@ -2435,7 +2427,7 @@
       <c r="AA21" s="2">
         <v>0</v>
       </c>
-      <c r="AB21" s="6">
+      <c r="AB21" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
@@ -2522,7 +2514,7 @@
       <c r="AA22" s="2">
         <v>1</v>
       </c>
-      <c r="AB22" s="6">
+      <c r="AB22" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -2609,7 +2601,7 @@
       <c r="AA23" s="2">
         <v>2</v>
       </c>
-      <c r="AB23" s="6">
+      <c r="AB23" s="2">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
@@ -2696,7 +2688,7 @@
       <c r="AA24" s="2">
         <v>1</v>
       </c>
-      <c r="AB24" s="6">
+      <c r="AB24" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
@@ -2783,7 +2775,7 @@
       <c r="AA25" s="2">
         <v>1</v>
       </c>
-      <c r="AB25" s="6">
+      <c r="AB25" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -2870,7 +2862,7 @@
       <c r="AA26" s="2">
         <v>2</v>
       </c>
-      <c r="AB26" s="6">
+      <c r="AB26" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
@@ -2957,7 +2949,7 @@
       <c r="AA27" s="2">
         <v>0</v>
       </c>
-      <c r="AB27" s="6">
+      <c r="AB27" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
@@ -3044,7 +3036,7 @@
       <c r="AA28" s="2">
         <v>2</v>
       </c>
-      <c r="AB28" s="6">
+      <c r="AB28" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
@@ -3131,7 +3123,7 @@
       <c r="AA29" s="2">
         <v>-1</v>
       </c>
-      <c r="AB29" s="6">
+      <c r="AB29" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
@@ -3218,7 +3210,7 @@
       <c r="AA30" s="2">
         <v>0</v>
       </c>
-      <c r="AB30" s="6">
+      <c r="AB30" s="2">
         <f t="shared" si="0"/>
         <v>-2</v>
       </c>
@@ -3305,7 +3297,7 @@
       <c r="AA31" s="2">
         <v>1</v>
       </c>
-      <c r="AB31" s="6">
+      <c r="AB31" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
@@ -3392,7 +3384,7 @@
       <c r="AA32" s="2">
         <v>1</v>
       </c>
-      <c r="AB32" s="6">
+      <c r="AB32" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
@@ -3479,7 +3471,7 @@
       <c r="AA33" s="2">
         <v>4</v>
       </c>
-      <c r="AB33" s="6">
+      <c r="AB33" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
@@ -3566,7 +3558,7 @@
       <c r="AA34" s="2">
         <v>3</v>
       </c>
-      <c r="AB34" s="6">
+      <c r="AB34" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
@@ -3653,7 +3645,7 @@
       <c r="AA35" s="2">
         <v>0</v>
       </c>
-      <c r="AB35" s="6">
+      <c r="AB35" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -3740,7 +3732,7 @@
       <c r="AA36" s="2">
         <v>3</v>
       </c>
-      <c r="AB36" s="6">
+      <c r="AB36" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
@@ -3827,7 +3819,7 @@
       <c r="AA37" s="2">
         <v>1</v>
       </c>
-      <c r="AB37" s="6">
+      <c r="AB37" s="2">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
@@ -3934,7 +3926,7 @@
       </c>
     </row>
     <row r="39" spans="1:28">
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="2" t="s">
         <v>4</v>
       </c>
       <c r="D39" s="2">
@@ -4035,7 +4027,7 @@
       </c>
     </row>
     <row r="40" spans="1:28">
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="2">
